--- a/Методы и средства криптографической защ инф/Лаба 2/Лаба 2.xlsx
+++ b/Методы и средства криптографической защ инф/Лаба 2/Лаба 2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ForMi\OneDrive\Desktop\Fourth_course\Методы и средства криптографической защ инф\Лаба 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE5F2218-87C3-4A28-ADDE-C87371CEDA31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42291BD0-A6A8-438F-8EA1-0F14F7C3938C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B8459DC6-B47A-44D9-8C4F-B46616E9EDDB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{B8459DC6-B47A-44D9-8C4F-B46616E9EDDB}"/>
   </bookViews>
   <sheets>
     <sheet name="Цезаря" sheetId="1" r:id="rId1"/>
@@ -158,7 +158,7 @@
     <t>2t+4 mod 33</t>
   </si>
   <si>
-    <t>ЖЭЪЖЫ СХУЯХ ЯГФНЧ - ЯНГЕНЕЪЖЯБН ЛЖХСНЯХН</t>
+    <t>ЖЭЪЖЫ СХУЯХ ЯДФНЧ - ЯНГЕНЕЪЗЯБН ЛЗХСНЯХН</t>
   </si>
 </sst>
 </file>
@@ -1303,13 +1303,13 @@
     </row>
     <row r="5" spans="2:35" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>10</v>
@@ -1402,6 +1402,140 @@
         <v>2</v>
       </c>
       <c r="AI5" s="7"/>
+    </row>
+    <row r="6" spans="2:35" x14ac:dyDescent="0.25">
+      <c r="B6">
+        <f>MOD(2*B3+4,33)</f>
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <f t="shared" ref="C6:AH6" si="1">MOD(2*C3+4,33)</f>
+        <v>6</v>
+      </c>
+      <c r="D6">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="E6">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="F6">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="G6">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="H6">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="I6">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="J6">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="K6">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="L6">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+      <c r="M6">
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="N6">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="O6">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="P6">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+      <c r="Q6">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="R6">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="S6">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="T6">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="U6">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="V6">
+        <f t="shared" si="1"/>
+        <v>11</v>
+      </c>
+      <c r="W6">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="X6">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="Y6">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="Z6">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="AA6">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="AB6">
+        <f t="shared" si="1"/>
+        <v>23</v>
+      </c>
+      <c r="AC6">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="AD6">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="AE6">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+      <c r="AF6">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+      <c r="AG6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH6">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
     </row>
     <row r="7" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B7" s="6" t="s">

--- a/Методы и средства криптографической защ инф/Лаба 2/Лаба 2.xlsx
+++ b/Методы и средства криптографической защ инф/Лаба 2/Лаба 2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ForMi\OneDrive\Desktop\Fourth_course\Методы и средства криптографической защ инф\Лаба 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42291BD0-A6A8-438F-8EA1-0F14F7C3938C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AE1F0E0-3AE9-41EF-B4AD-FB2695255CF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{B8459DC6-B47A-44D9-8C4F-B46616E9EDDB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{B8459DC6-B47A-44D9-8C4F-B46616E9EDDB}"/>
   </bookViews>
   <sheets>
     <sheet name="Цезаря" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="44">
   <si>
     <t>А</t>
   </si>
@@ -159,6 +159,18 @@
   </si>
   <si>
     <t>ЖЭЪЖЫ СХУЯХ ЯДФНЧ - ЯНГЕНЕЪЗЯБН ЛЗХСНЯХН</t>
+  </si>
+  <si>
+    <t>РАЗУМА ЛИШАЕТ НЕ СОМНЕНИЕ, А УВЕРЕННОСТЬ</t>
+  </si>
+  <si>
+    <t>Вариант 7: k = 7, ключевое слово</t>
+  </si>
+  <si>
+    <t>ОСЕНЬ</t>
+  </si>
+  <si>
+    <t>ЁШСИБШ АЕПШЮЗ ВЮ ЖГБВЮВЕЮ, Ш ИЪЮЁЮВВГЖЗФ</t>
   </si>
 </sst>
 </file>
@@ -363,6 +375,64 @@
         <a:xfrm>
           <a:off x="4132384" y="1436076"/>
           <a:ext cx="0" cy="271097"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>212481</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>21981</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>212481</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>175846</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="3" name="Прямая со стрелкой 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5EC72E07-DD7A-E425-668B-E377086D9FB9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4557346" y="1355481"/>
+          <a:ext cx="0" cy="344365"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -1625,10 +1695,453 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A99A8804-015A-48C0-86E5-6FA3E60E7405}">
-  <dimension ref="A1"/>
+  <dimension ref="B2:AH10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="2" max="34" width="3.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:34" x14ac:dyDescent="0.25">
+      <c r="B2" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
+    </row>
+    <row r="3" spans="2:34" x14ac:dyDescent="0.25">
+      <c r="B3" s="2">
+        <v>0</v>
+      </c>
+      <c r="C3" s="2">
+        <f>B3+1</f>
+        <v>1</v>
+      </c>
+      <c r="D3" s="2">
+        <f t="shared" ref="D3:AH3" si="0">C3+1</f>
+        <v>2</v>
+      </c>
+      <c r="E3" s="2">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="F3" s="2">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G3" s="2">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="H3" s="2">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="I3" s="2">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="J3" s="2">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="K3" s="2">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="L3" s="2">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="M3" s="2">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="N3" s="2">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="O3" s="2">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="P3" s="2">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="Q3" s="2">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="R3" s="2">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="S3" s="2">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="T3" s="2">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="U3" s="2">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="V3" s="2">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="W3" s="2">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="X3" s="2">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="Y3" s="2">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="Z3" s="2">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="AA3" s="2">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="AB3" s="2">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="AC3" s="2">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="AD3" s="2">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="AE3" s="2">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="AF3" s="2">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="AG3" s="2">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="AH3" s="2">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="2:34" x14ac:dyDescent="0.25">
+      <c r="B4" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="R4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="S4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="T4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="U4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="V4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="W4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="X4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="AA4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="AE4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="AF4" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="AG4" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="AH4" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="2:34" x14ac:dyDescent="0.25">
+      <c r="B5" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P5" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="R5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="S5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="T5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="U5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="V5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="W5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="X5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="Y5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AA5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AC5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AD5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="AE5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AF5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="AG5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AH5" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="2:34" x14ac:dyDescent="0.25">
+      <c r="B7" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="6"/>
+      <c r="M7" s="6"/>
+      <c r="N7" s="6"/>
+      <c r="O7" s="6"/>
+      <c r="P7" s="6"/>
+      <c r="Q7" s="6"/>
+      <c r="R7" s="6"/>
+      <c r="S7" s="6"/>
+      <c r="T7" s="6"/>
+      <c r="U7" s="6"/>
+      <c r="V7" s="6"/>
+      <c r="W7" s="6"/>
+      <c r="X7" s="6"/>
+      <c r="Y7" s="6"/>
+      <c r="Z7" s="6"/>
+      <c r="AA7" s="6"/>
+      <c r="AB7" s="6"/>
+      <c r="AC7" s="6"/>
+      <c r="AD7" s="6"/>
+      <c r="AE7" s="6"/>
+      <c r="AF7" s="6"/>
+      <c r="AG7" s="6"/>
+      <c r="AH7" s="6"/>
+    </row>
+    <row r="10" spans="2:34" x14ac:dyDescent="0.25">
+      <c r="B10" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6"/>
+      <c r="I10" s="6"/>
+      <c r="J10" s="6"/>
+      <c r="K10" s="6"/>
+      <c r="L10" s="6"/>
+      <c r="M10" s="6"/>
+      <c r="N10" s="6"/>
+      <c r="O10" s="6"/>
+      <c r="P10" s="6"/>
+      <c r="Q10" s="6"/>
+      <c r="R10" s="6"/>
+      <c r="S10" s="6"/>
+      <c r="T10" s="6"/>
+      <c r="U10" s="6"/>
+      <c r="V10" s="6"/>
+      <c r="W10" s="6"/>
+      <c r="X10" s="6"/>
+      <c r="Y10" s="6"/>
+      <c r="Z10" s="6"/>
+      <c r="AA10" s="6"/>
+      <c r="AB10" s="6"/>
+      <c r="AC10" s="6"/>
+      <c r="AD10" s="6"/>
+      <c r="AE10" s="6"/>
+      <c r="AF10" s="6"/>
+      <c r="AG10" s="6"/>
+      <c r="AH10" s="6"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="B2:N2"/>
+    <mergeCell ref="O2:R2"/>
+    <mergeCell ref="B7:AH7"/>
+    <mergeCell ref="B10:AH10"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/Методы и средства криптографической защ инф/Лаба 2/Лаба 2.xlsx
+++ b/Методы и средства криптографической защ инф/Лаба 2/Лаба 2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ForMi\OneDrive\Desktop\Fourth_course\Методы и средства криптографической защ инф\Лаба 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AE1F0E0-3AE9-41EF-B4AD-FB2695255CF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{858F1003-84B4-4BB1-A1AA-11D350CBC0DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{B8459DC6-B47A-44D9-8C4F-B46616E9EDDB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{B8459DC6-B47A-44D9-8C4F-B46616E9EDDB}"/>
   </bookViews>
   <sheets>
     <sheet name="Цезаря" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="47">
   <si>
     <t>А</t>
   </si>
@@ -171,6 +171,15 @@
   </si>
   <si>
     <t>ЁШСИБШ АЕПШЮЗ ВЮ ЖГБВЮВЕЮ, Ш ИЪЮЁЮВВГЖЗФ</t>
+  </si>
+  <si>
+    <t>Вариант 7: ключевое слово</t>
+  </si>
+  <si>
+    <t>УСПЕХ – ЭТО КОГДА ТЫ ДЕВЯТЬ РАЗ УПАЛ, НО ДЕСЯТЬ РАЗ ПОДНЯЛСЯ</t>
+  </si>
+  <si>
+    <t>ЫДШЖЮ - АЪГ ХГМПЙ ЪЬ ПЖЛВЪИ ЩЙТ ЫШЙЦ, ЗГ ПЖДВЪИ ЩЙТ ШГПЗВЦДВ</t>
   </si>
 </sst>
 </file>
@@ -211,7 +220,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -243,11 +252,31 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -270,6 +299,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -433,6 +469,64 @@
         <a:xfrm>
           <a:off x="4557346" y="1355481"/>
           <a:ext cx="0" cy="344365"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>600808</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>14654</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>600808</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="3" name="Прямая со стрелкой 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7EF2DF82-ECFE-5B4B-6CD8-D83C6F6ACC7A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3033346" y="2110154"/>
+          <a:ext cx="0" cy="366346"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -2147,9 +2241,336 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9413EA7B-8C41-4159-9AA5-921F64C50861}">
-  <dimension ref="A1"/>
+  <dimension ref="B5:S14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <sheetData>
+    <row r="5" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B5" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="8"/>
+      <c r="K5" s="8"/>
+      <c r="L5" s="8"/>
+      <c r="M5" s="8"/>
+      <c r="N5" s="8"/>
+      <c r="O5" s="9"/>
+      <c r="P5" s="9"/>
+      <c r="Q5" s="9"/>
+      <c r="R5" s="9"/>
+    </row>
+    <row r="6" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="K6" s="11">
+        <v>0</v>
+      </c>
+      <c r="L6" s="12">
+        <v>1</v>
+      </c>
+      <c r="M6" s="12">
+        <v>2</v>
+      </c>
+      <c r="N6" s="12">
+        <v>3</v>
+      </c>
+      <c r="O6" s="12">
+        <v>4</v>
+      </c>
+      <c r="P6" s="12">
+        <v>5</v>
+      </c>
+      <c r="Q6" s="12">
+        <v>6</v>
+      </c>
+      <c r="R6" s="12">
+        <v>7</v>
+      </c>
+      <c r="S6" s="12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K7" s="10">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <f t="shared" ref="L7:R7" si="0">$K7*L$6+L$6-1</f>
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="N7">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="O7">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="P7">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="Q7">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="R7">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="S7">
+        <f>$K7*S$6+S$6-1</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K8" s="10">
+        <v>1</v>
+      </c>
+      <c r="L8">
+        <f>$K8*8+L$6-1</f>
+        <v>8</v>
+      </c>
+      <c r="M8">
+        <f t="shared" ref="M8:S10" si="1">$K8*8+M$6-1</f>
+        <v>9</v>
+      </c>
+      <c r="N8">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="O8">
+        <f t="shared" si="1"/>
+        <v>11</v>
+      </c>
+      <c r="P8">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="Q8">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="R8">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="S8">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="K9" s="10">
+        <v>2</v>
+      </c>
+      <c r="L9">
+        <f t="shared" ref="L9:L10" si="2">$K9*8+L$6-1</f>
+        <v>16</v>
+      </c>
+      <c r="M9">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="N9">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="O9">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="P9">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="Q9">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="R9">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="S9">
+        <f t="shared" si="1"/>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="K10" s="10">
+        <v>3</v>
+      </c>
+      <c r="L10">
+        <f t="shared" si="2"/>
+        <v>24</v>
+      </c>
+      <c r="M10">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="N10">
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="O10">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="P10">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="Q10">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+      <c r="R10">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="S10">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B11" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="6"/>
+    </row>
+    <row r="14" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B14" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6"/>
+      <c r="I14" s="6"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="O5:R5"/>
+    <mergeCell ref="B11:I11"/>
+    <mergeCell ref="B14:I14"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Методы и средства криптографической защ инф/Лаба 2/Лаба 2.xlsx
+++ b/Методы и средства криптографической защ инф/Лаба 2/Лаба 2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ForMi\OneDrive\Desktop\Fourth_course\Методы и средства криптографической защ инф\Лаба 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{858F1003-84B4-4BB1-A1AA-11D350CBC0DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26B4FE5E-7389-4711-B586-3CE3DBDAB867}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{B8459DC6-B47A-44D9-8C4F-B46616E9EDDB}"/>
+    <workbookView xWindow="7200" yWindow="2640" windowWidth="21600" windowHeight="11295" activeTab="3" xr2:uid="{B8459DC6-B47A-44D9-8C4F-B46616E9EDDB}"/>
   </bookViews>
   <sheets>
     <sheet name="Цезаря" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="49">
   <si>
     <t>А</t>
   </si>
@@ -180,6 +180,12 @@
   </si>
   <si>
     <t>ЫДШЖЮ - АЪГ ХГМПЙ ЪЬ ПЖЛВЪИ ЩЙТ ЫШЙЦ, ЗГ ПЖДВЪИ ЩЙТ ШГПЗВЦДВ</t>
+  </si>
+  <si>
+    <t>Открытый текст:</t>
+  </si>
+  <si>
+    <t>Результат:</t>
   </si>
 </sst>
 </file>
@@ -276,7 +282,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -284,6 +290,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -299,13 +314,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -329,14 +341,14 @@
     <xdr:from>
       <xdr:col>16</xdr:col>
       <xdr:colOff>7327</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:row>7</xdr:row>
       <xdr:rowOff>80596</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>7327</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>87923</xdr:rowOff>
+      <xdr:rowOff>117231</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -351,8 +363,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3040673" y="1223596"/>
-          <a:ext cx="0" cy="388327"/>
+          <a:off x="3040673" y="1414096"/>
+          <a:ext cx="0" cy="227135"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -385,16 +397,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>7326</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>51288</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>7327</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>29307</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>7326</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>131885</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>7327</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>109904</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -409,7 +421,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4132384" y="1436076"/>
+          <a:off x="2154115" y="1604595"/>
           <a:ext cx="0" cy="271097"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
@@ -443,16 +455,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>212481</xdr:colOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>205154</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>21981</xdr:rowOff>
+      <xdr:rowOff>14654</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>212481</xdr:colOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>205154</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>175846</xdr:rowOff>
+      <xdr:rowOff>168519</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -467,7 +479,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4557346" y="1355481"/>
+          <a:off x="2351942" y="1348154"/>
           <a:ext cx="0" cy="344365"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
@@ -872,7 +884,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68DA4A81-55F3-481A-A438-E457AE834B17}">
-  <dimension ref="B2:AI10"/>
+  <dimension ref="B2:AI11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="2.7109375" bestFit="1" customWidth="1"/>
@@ -899,21 +911,22 @@
     <col min="32" max="32" width="2.42578125" bestFit="1" customWidth="1"/>
     <col min="33" max="33" width="2.85546875" bestFit="1" customWidth="1"/>
     <col min="34" max="34" width="2.140625" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="2.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:35" x14ac:dyDescent="0.25">
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="8"/>
+      <c r="I2" s="8"/>
+      <c r="J2" s="8"/>
+      <c r="K2" s="8"/>
     </row>
     <row r="3" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
@@ -1015,7 +1028,7 @@
       <c r="AH3" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AI3" s="5">
+      <c r="AI3" s="10">
         <v>7</v>
       </c>
     </row>
@@ -1119,87 +1132,98 @@
       <c r="AH4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="AI4" s="5"/>
+      <c r="AI4" s="10"/>
     </row>
     <row r="6" spans="2:35" x14ac:dyDescent="0.25">
-      <c r="B6" s="4" t="s">
+      <c r="B6" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="7" spans="2:35" x14ac:dyDescent="0.25">
+      <c r="B7" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4"/>
-      <c r="K6" s="4"/>
-      <c r="L6" s="4"/>
-      <c r="M6" s="4"/>
-      <c r="N6" s="4"/>
-      <c r="O6" s="4"/>
-      <c r="P6" s="4"/>
-      <c r="Q6" s="4"/>
-      <c r="R6" s="4"/>
-      <c r="S6" s="4"/>
-      <c r="T6" s="4"/>
-      <c r="U6" s="4"/>
-      <c r="V6" s="4"/>
-      <c r="W6" s="4"/>
-      <c r="X6" s="4"/>
-      <c r="Y6" s="4"/>
-      <c r="Z6" s="4"/>
-      <c r="AA6" s="4"/>
-      <c r="AB6" s="4"/>
-      <c r="AC6" s="4"/>
-      <c r="AD6" s="4"/>
-      <c r="AE6" s="4"/>
-      <c r="AF6" s="4"/>
-      <c r="AG6" s="4"/>
-      <c r="AH6" s="4"/>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="9"/>
+      <c r="N7" s="9"/>
+      <c r="O7" s="9"/>
+      <c r="P7" s="9"/>
+      <c r="Q7" s="9"/>
+      <c r="R7" s="9"/>
+      <c r="S7" s="9"/>
+      <c r="T7" s="9"/>
+      <c r="U7" s="9"/>
+      <c r="V7" s="9"/>
+      <c r="W7" s="9"/>
+      <c r="X7" s="9"/>
+      <c r="Y7" s="9"/>
+      <c r="Z7" s="9"/>
+      <c r="AA7" s="9"/>
+      <c r="AB7" s="9"/>
+      <c r="AC7" s="9"/>
+      <c r="AD7" s="9"/>
+      <c r="AE7" s="9"/>
+      <c r="AF7" s="9"/>
+      <c r="AG7" s="9"/>
+      <c r="AH7" s="9"/>
+    </row>
+    <row r="9" spans="2:35" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="10" spans="2:35" x14ac:dyDescent="0.25">
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="4"/>
-      <c r="J10" s="4"/>
-      <c r="K10" s="4"/>
-      <c r="L10" s="4"/>
-      <c r="M10" s="4"/>
-      <c r="N10" s="4"/>
-      <c r="O10" s="4"/>
-      <c r="P10" s="4"/>
-      <c r="Q10" s="4"/>
-      <c r="R10" s="4"/>
-      <c r="S10" s="4"/>
-      <c r="T10" s="4"/>
-      <c r="U10" s="4"/>
-      <c r="V10" s="4"/>
-      <c r="W10" s="4"/>
-      <c r="X10" s="4"/>
-      <c r="Y10" s="4"/>
-      <c r="Z10" s="4"/>
-      <c r="AA10" s="4"/>
-      <c r="AB10" s="4"/>
-      <c r="AC10" s="4"/>
-      <c r="AD10" s="4"/>
-      <c r="AE10" s="4"/>
-      <c r="AF10" s="4"/>
-      <c r="AG10" s="4"/>
-      <c r="AH10" s="4"/>
+    </row>
+    <row r="11" spans="2:35" x14ac:dyDescent="0.25">
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3"/>
+      <c r="J11" s="3"/>
+      <c r="K11" s="3"/>
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
+      <c r="N11" s="3"/>
+      <c r="O11" s="3"/>
+      <c r="P11" s="3"/>
+      <c r="Q11" s="3"/>
+      <c r="R11" s="3"/>
+      <c r="S11" s="3"/>
+      <c r="T11" s="3"/>
+      <c r="U11" s="3"/>
+      <c r="V11" s="3"/>
+      <c r="W11" s="3"/>
+      <c r="X11" s="3"/>
+      <c r="Y11" s="3"/>
+      <c r="Z11" s="3"/>
+      <c r="AA11" s="3"/>
+      <c r="AB11" s="3"/>
+      <c r="AC11" s="3"/>
+      <c r="AD11" s="3"/>
+      <c r="AE11" s="3"/>
+      <c r="AF11" s="3"/>
+      <c r="AG11" s="3"/>
+      <c r="AH11" s="3"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="B2:K2"/>
-    <mergeCell ref="B6:AH6"/>
-    <mergeCell ref="B10:AH10"/>
+    <mergeCell ref="B7:AH7"/>
     <mergeCell ref="AI3:AI4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1209,23 +1233,23 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE566223-60A0-4B00-B1B1-5542EDD82243}">
-  <dimension ref="B2:AI10"/>
+  <dimension ref="B2:AI11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="34" width="3.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:35" x14ac:dyDescent="0.25">
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="8"/>
+      <c r="I2" s="8"/>
     </row>
     <row r="3" spans="2:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="2">
@@ -1359,7 +1383,7 @@
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="AI3" s="7" t="s">
+      <c r="AI3" s="12" t="s">
         <v>38</v>
       </c>
     </row>
@@ -1463,7 +1487,7 @@
       <c r="AH4" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="AI4" s="7"/>
+      <c r="AI4" s="12"/>
     </row>
     <row r="5" spans="2:35" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
@@ -1565,7 +1589,7 @@
       <c r="AH5" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="AI5" s="7"/>
+      <c r="AI5" s="12"/>
     </row>
     <row r="6" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B6">
@@ -1702,83 +1726,91 @@
       </c>
     </row>
     <row r="7" spans="2:35" x14ac:dyDescent="0.25">
-      <c r="B7" s="6" t="s">
+      <c r="B7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8" spans="2:35" x14ac:dyDescent="0.25">
+      <c r="B8" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="6"/>
-      <c r="J7" s="6"/>
-      <c r="K7" s="6"/>
-      <c r="L7" s="6"/>
-      <c r="M7" s="6"/>
-      <c r="N7" s="6"/>
-      <c r="O7" s="6"/>
-      <c r="P7" s="6"/>
-      <c r="Q7" s="6"/>
-      <c r="R7" s="6"/>
-      <c r="S7" s="6"/>
-      <c r="T7" s="6"/>
-      <c r="U7" s="6"/>
-      <c r="V7" s="6"/>
-      <c r="W7" s="6"/>
-      <c r="X7" s="6"/>
-      <c r="Y7" s="6"/>
-      <c r="Z7" s="6"/>
-      <c r="AA7" s="6"/>
-      <c r="AB7" s="6"/>
-      <c r="AC7" s="6"/>
-      <c r="AD7" s="6"/>
-      <c r="AE7" s="6"/>
-      <c r="AF7" s="6"/>
-      <c r="AG7" s="6"/>
-      <c r="AH7" s="6"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="13"/>
+      <c r="G8" s="13"/>
+      <c r="H8" s="13"/>
+      <c r="I8" s="13"/>
+      <c r="J8" s="13"/>
+      <c r="K8" s="13"/>
+      <c r="L8" s="13"/>
+      <c r="M8" s="13"/>
+      <c r="N8" s="13"/>
+      <c r="O8" s="13"/>
+      <c r="P8" s="13"/>
+      <c r="Q8" s="13"/>
+      <c r="R8" s="13"/>
+      <c r="S8" s="13"/>
+      <c r="T8" s="13"/>
+      <c r="U8" s="13"/>
+      <c r="V8" s="13"/>
+      <c r="W8" s="13"/>
+      <c r="X8" s="13"/>
+      <c r="Y8" s="13"/>
+      <c r="Z8" s="13"/>
+      <c r="AA8" s="13"/>
+      <c r="AB8" s="13"/>
+      <c r="AC8" s="13"/>
+      <c r="AD8" s="13"/>
+      <c r="AE8" s="13"/>
+      <c r="AF8" s="13"/>
+      <c r="AG8" s="13"/>
+      <c r="AH8" s="13"/>
     </row>
     <row r="10" spans="2:35" x14ac:dyDescent="0.25">
-      <c r="B10" s="6" t="s">
+      <c r="B10" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="11" spans="2:35" x14ac:dyDescent="0.25">
+      <c r="B11" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6"/>
-      <c r="I10" s="6"/>
-      <c r="J10" s="6"/>
-      <c r="K10" s="6"/>
-      <c r="L10" s="6"/>
-      <c r="M10" s="6"/>
-      <c r="N10" s="6"/>
-      <c r="O10" s="6"/>
-      <c r="P10" s="6"/>
-      <c r="Q10" s="6"/>
-      <c r="R10" s="6"/>
-      <c r="S10" s="6"/>
-      <c r="T10" s="6"/>
-      <c r="U10" s="6"/>
-      <c r="V10" s="6"/>
-      <c r="W10" s="6"/>
-      <c r="X10" s="6"/>
-      <c r="Y10" s="6"/>
-      <c r="Z10" s="6"/>
-      <c r="AA10" s="6"/>
-      <c r="AB10" s="6"/>
-      <c r="AC10" s="6"/>
-      <c r="AD10" s="6"/>
-      <c r="AE10" s="6"/>
-      <c r="AF10" s="6"/>
-      <c r="AG10" s="6"/>
-      <c r="AH10" s="6"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="K11" s="4"/>
+      <c r="L11" s="4"/>
+      <c r="M11" s="4"/>
+      <c r="N11" s="4"/>
+      <c r="O11" s="4"/>
+      <c r="P11" s="4"/>
+      <c r="Q11" s="4"/>
+      <c r="R11" s="4"/>
+      <c r="S11" s="4"/>
+      <c r="T11" s="4"/>
+      <c r="U11" s="4"/>
+      <c r="V11" s="4"/>
+      <c r="W11" s="4"/>
+      <c r="X11" s="4"/>
+      <c r="Y11" s="4"/>
+      <c r="Z11" s="4"/>
+      <c r="AA11" s="4"/>
+      <c r="AB11" s="4"/>
+      <c r="AC11" s="4"/>
+      <c r="AD11" s="4"/>
+      <c r="AE11" s="4"/>
+      <c r="AF11" s="4"/>
+      <c r="AG11" s="4"/>
+      <c r="AH11" s="4"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="B10:AH10"/>
-    <mergeCell ref="B7:AH7"/>
+  <mergeCells count="2">
     <mergeCell ref="B2:I2"/>
     <mergeCell ref="AI3:AI5"/>
   </mergeCells>
@@ -1796,27 +1828,27 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:34" x14ac:dyDescent="0.25">
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
-      <c r="N2" s="3"/>
-      <c r="O2" s="3" t="s">
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="8"/>
+      <c r="I2" s="8"/>
+      <c r="J2" s="8"/>
+      <c r="K2" s="8"/>
+      <c r="L2" s="8"/>
+      <c r="M2" s="8"/>
+      <c r="N2" s="8"/>
+      <c r="O2" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="P2" s="3"/>
-      <c r="Q2" s="3"/>
-      <c r="R2" s="3"/>
+      <c r="P2" s="8"/>
+      <c r="Q2" s="8"/>
+      <c r="R2" s="8"/>
     </row>
     <row r="3" spans="2:34" x14ac:dyDescent="0.25">
       <c r="B3" s="2">
@@ -2153,86 +2185,94 @@
         <v>24</v>
       </c>
     </row>
+    <row r="6" spans="2:34" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>47</v>
+      </c>
+    </row>
     <row r="7" spans="2:34" x14ac:dyDescent="0.25">
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="6"/>
-      <c r="J7" s="6"/>
-      <c r="K7" s="6"/>
-      <c r="L7" s="6"/>
-      <c r="M7" s="6"/>
-      <c r="N7" s="6"/>
-      <c r="O7" s="6"/>
-      <c r="P7" s="6"/>
-      <c r="Q7" s="6"/>
-      <c r="R7" s="6"/>
-      <c r="S7" s="6"/>
-      <c r="T7" s="6"/>
-      <c r="U7" s="6"/>
-      <c r="V7" s="6"/>
-      <c r="W7" s="6"/>
-      <c r="X7" s="6"/>
-      <c r="Y7" s="6"/>
-      <c r="Z7" s="6"/>
-      <c r="AA7" s="6"/>
-      <c r="AB7" s="6"/>
-      <c r="AC7" s="6"/>
-      <c r="AD7" s="6"/>
-      <c r="AE7" s="6"/>
-      <c r="AF7" s="6"/>
-      <c r="AG7" s="6"/>
-      <c r="AH7" s="6"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="13"/>
+      <c r="F7" s="13"/>
+      <c r="G7" s="13"/>
+      <c r="H7" s="13"/>
+      <c r="I7" s="13"/>
+      <c r="J7" s="13"/>
+      <c r="K7" s="13"/>
+      <c r="L7" s="13"/>
+      <c r="M7" s="13"/>
+      <c r="N7" s="13"/>
+      <c r="O7" s="13"/>
+      <c r="P7" s="13"/>
+      <c r="Q7" s="13"/>
+      <c r="R7" s="13"/>
+      <c r="S7" s="13"/>
+      <c r="T7" s="13"/>
+      <c r="U7" s="13"/>
+      <c r="V7" s="13"/>
+      <c r="W7" s="13"/>
+      <c r="X7" s="13"/>
+      <c r="Y7" s="13"/>
+      <c r="Z7" s="13"/>
+      <c r="AA7" s="13"/>
+      <c r="AB7" s="13"/>
+      <c r="AC7" s="13"/>
+      <c r="AD7" s="13"/>
+      <c r="AE7" s="13"/>
+      <c r="AF7" s="13"/>
+      <c r="AG7" s="13"/>
+      <c r="AH7" s="13"/>
+    </row>
+    <row r="9" spans="2:34" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="10" spans="2:34" x14ac:dyDescent="0.25">
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6"/>
-      <c r="I10" s="6"/>
-      <c r="J10" s="6"/>
-      <c r="K10" s="6"/>
-      <c r="L10" s="6"/>
-      <c r="M10" s="6"/>
-      <c r="N10" s="6"/>
-      <c r="O10" s="6"/>
-      <c r="P10" s="6"/>
-      <c r="Q10" s="6"/>
-      <c r="R10" s="6"/>
-      <c r="S10" s="6"/>
-      <c r="T10" s="6"/>
-      <c r="U10" s="6"/>
-      <c r="V10" s="6"/>
-      <c r="W10" s="6"/>
-      <c r="X10" s="6"/>
-      <c r="Y10" s="6"/>
-      <c r="Z10" s="6"/>
-      <c r="AA10" s="6"/>
-      <c r="AB10" s="6"/>
-      <c r="AC10" s="6"/>
-      <c r="AD10" s="6"/>
-      <c r="AE10" s="6"/>
-      <c r="AF10" s="6"/>
-      <c r="AG10" s="6"/>
-      <c r="AH10" s="6"/>
+      <c r="C10" s="13"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="13"/>
+      <c r="G10" s="13"/>
+      <c r="H10" s="13"/>
+      <c r="I10" s="13"/>
+      <c r="J10" s="13"/>
+      <c r="K10" s="13"/>
+      <c r="L10" s="13"/>
+      <c r="M10" s="13"/>
+      <c r="N10" s="13"/>
+      <c r="O10" s="13"/>
+      <c r="P10" s="13"/>
+      <c r="Q10" s="13"/>
+      <c r="R10" s="13"/>
+      <c r="S10" s="13"/>
+      <c r="T10" s="13"/>
+      <c r="U10" s="13"/>
+      <c r="V10" s="13"/>
+      <c r="W10" s="13"/>
+      <c r="X10" s="13"/>
+      <c r="Y10" s="13"/>
+      <c r="Z10" s="13"/>
+      <c r="AA10" s="13"/>
+      <c r="AB10" s="13"/>
+      <c r="AC10" s="13"/>
+      <c r="AD10" s="13"/>
+      <c r="AE10" s="13"/>
+      <c r="AF10" s="13"/>
+      <c r="AG10" s="13"/>
+      <c r="AH10" s="13"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="2">
     <mergeCell ref="B2:N2"/>
     <mergeCell ref="O2:R2"/>
-    <mergeCell ref="B7:AH7"/>
-    <mergeCell ref="B10:AH10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -2245,23 +2285,12 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="5" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B5" s="8" t="s">
+      <c r="B5" t="s">
         <v>44</v>
       </c>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8" t="s">
+      <c r="E5" t="s">
         <v>42</v>
       </c>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
-      <c r="H5" s="8"/>
-      <c r="I5" s="8"/>
-      <c r="J5" s="8"/>
-      <c r="K5" s="8"/>
-      <c r="L5" s="8"/>
-      <c r="M5" s="8"/>
-      <c r="N5" s="8"/>
       <c r="O5" s="9"/>
       <c r="P5" s="9"/>
       <c r="Q5" s="9"/>
@@ -2292,31 +2321,31 @@
       <c r="I6" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="K6" s="11">
+      <c r="K6" s="6">
         <v>0</v>
       </c>
-      <c r="L6" s="12">
+      <c r="L6" s="7">
         <v>1</v>
       </c>
-      <c r="M6" s="12">
+      <c r="M6" s="7">
         <v>2</v>
       </c>
-      <c r="N6" s="12">
+      <c r="N6" s="7">
         <v>3</v>
       </c>
-      <c r="O6" s="12">
+      <c r="O6" s="7">
         <v>4</v>
       </c>
-      <c r="P6" s="12">
+      <c r="P6" s="7">
         <v>5</v>
       </c>
-      <c r="Q6" s="12">
+      <c r="Q6" s="7">
         <v>6</v>
       </c>
-      <c r="R6" s="12">
+      <c r="R6" s="7">
         <v>7</v>
       </c>
-      <c r="S6" s="12">
+      <c r="S6" s="7">
         <v>8</v>
       </c>
     </row>
@@ -2345,7 +2374,7 @@
       <c r="I7" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="K7" s="10">
+      <c r="K7" s="5">
         <v>0</v>
       </c>
       <c r="L7">
@@ -2406,7 +2435,7 @@
       <c r="I8" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="K8" s="10">
+      <c r="K8" s="5">
         <v>1</v>
       </c>
       <c r="L8">
@@ -2467,7 +2496,7 @@
       <c r="I9" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="K9" s="10">
+      <c r="K9" s="5">
         <v>2</v>
       </c>
       <c r="L9">
@@ -2504,7 +2533,10 @@
       </c>
     </row>
     <row r="10" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="K10" s="10">
+      <c r="B10" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="K10" s="5">
         <v>3</v>
       </c>
       <c r="L10">
@@ -2541,28 +2573,33 @@
       </c>
     </row>
     <row r="11" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
-      <c r="I11" s="6"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="11"/>
+    </row>
+    <row r="13" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="14" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="3">
